--- a/06_코드/qa/manual_check/J5_수기검산_워크시트.xlsx
+++ b/06_코드/qa/manual_check/J5_수기검산_워크시트.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>d68425df597e</t>
+          <t>c7b88361e96c</t>
         </is>
       </c>
     </row>
@@ -1218,14 +1218,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1258,16 +1256,6 @@
           <t>② 근거 조항</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>코드 산출값</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>③ 일치?</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -1277,10 +1265,6 @@
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="8" t="n"/>
-      <c r="D5" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="E5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1290,10 +1274,6 @@
       </c>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="8" t="n"/>
-      <c r="D6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1303,10 +1283,6 @@
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
-      <c r="D7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1316,10 +1292,6 @@
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1329,8 +1301,6 @@
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
-      <c r="D9" s="10" t="inlineStr"/>
-      <c r="E9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1340,8 +1310,6 @@
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1351,10 +1319,6 @@
       </c>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="8" t="n"/>
-      <c r="D11" s="10" t="n">
-        <v>114229271088.8889</v>
-      </c>
-      <c r="E11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1364,10 +1328,6 @@
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="10" t="n">
-        <v>114229271088.8889</v>
-      </c>
-      <c r="E12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1377,10 +1337,6 @@
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="10" t="n">
-        <v>118</v>
-      </c>
-      <c r="E13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1390,12 +1346,6 @@
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>SEASONED</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1405,8 +1355,6 @@
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
-      <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1426,6 +1374,13 @@
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>※ 90일 원자료는 '2b_L2_원자료' 시트에 있다. SUM·COUNTIF 로 직접 집계할 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>※ 코드 산출값은 J5_코드값_봉인.xlsx 에 있다. 이 시트를 다 채운 뒤에 열 것.</t>
         </is>
       </c>
     </row>
@@ -3224,14 +3179,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -3272,42 +3227,42 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>코드 ADTV90</t>
+          <t>① 내 ADTV90</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>코드 시즈닝</t>
+          <t>② 내 시즈닝일수</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>① 하한 통과?</t>
+          <t>③ 하한 통과?</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>② 시즈닝 통과?</t>
+          <t>④ 시즈닝 통과?</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>③ 편입?</t>
+          <t>⑤ 편입?</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>④ 제외사유</t>
+          <t>⑥ 제외사유</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>⑤ 셀</t>
+          <t>⑦ 셀</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>⑥ 최종비중</t>
+          <t>⑧ 최종비중</t>
         </is>
       </c>
     </row>
@@ -3327,12 +3282,8 @@
           <t>AI_ROBOTICS</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>34301690381.37778</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>118</v>
-      </c>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
       <c r="F5" s="8" t="n"/>
       <c r="G5" s="8" t="n"/>
       <c r="H5" s="8" t="n"/>
@@ -3356,12 +3307,8 @@
           <t>AI_ROBOTICS</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>83817198012.22223</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>118</v>
-      </c>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
       <c r="H6" s="8" t="n"/>
@@ -3385,12 +3332,8 @@
           <t>AI_ROBOTICS</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>133478399757.7778</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>118</v>
-      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
       <c r="H7" s="8" t="n"/>
@@ -3414,12 +3357,8 @@
           <t>ENERGY_POWER</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
-        <v>114229271088.8889</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>118</v>
-      </c>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n"/>
@@ -3443,12 +3382,8 @@
           <t>ENERGY_POWER</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>141170088695.0444</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>118</v>
-      </c>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
       <c r="H9" s="8" t="n"/>
@@ -3472,12 +3407,8 @@
           <t>ENERGY_POWER</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>132869683521.3222</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>118</v>
-      </c>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="8" t="n"/>
@@ -3501,12 +3432,8 @@
           <t>SPACE_DEFENSE</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>322298375954.8222</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>118</v>
-      </c>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
       <c r="H11" s="8" t="n"/>
@@ -3530,12 +3457,8 @@
           <t>SPACE_DEFENSE</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>172106781525.1111</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>118</v>
-      </c>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="8" t="n"/>
@@ -3559,12 +3482,8 @@
           <t>SPACE_DEFENSE</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
-        <v>170174931845.4</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>118</v>
-      </c>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
       <c r="H13" s="8" t="n"/>
@@ -3588,12 +3507,8 @@
           <t>AI_ROBOTICS</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
-        <v>785609104.1944444</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>125</v>
-      </c>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
@@ -3617,12 +3532,8 @@
           <t>AI_ROBOTICS</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>1000675328.622222</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>125</v>
-      </c>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="n"/>
@@ -3646,12 +3557,8 @@
           <t>AI_ROBOTICS</t>
         </is>
       </c>
-      <c r="D16" s="9" t="n">
-        <v>841837201.5555556</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>125</v>
-      </c>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
@@ -3675,12 +3582,8 @@
           <t>ENERGY_POWER</t>
         </is>
       </c>
-      <c r="D17" s="9" t="n">
-        <v>1323863165.211111</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>125</v>
-      </c>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="n"/>
@@ -3704,12 +3607,8 @@
           <t>ENERGY_POWER</t>
         </is>
       </c>
-      <c r="D18" s="9" t="n">
-        <v>1025620637.122222</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>125</v>
-      </c>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
@@ -3733,12 +3632,8 @@
           <t>ENERGY_POWER</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n">
-        <v>2212006842.211111</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>125</v>
-      </c>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
@@ -3762,12 +3657,8 @@
           <t>SPACE_DEFENSE</t>
         </is>
       </c>
-      <c r="D20" s="9" t="n">
-        <v>243924255.8333333</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>125</v>
-      </c>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
@@ -3791,12 +3682,8 @@
           <t>SPACE_DEFENSE</t>
         </is>
       </c>
-      <c r="D21" s="11" t="n">
-        <v>336854177.6222222</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>125</v>
-      </c>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
@@ -3820,10 +3707,8 @@
           <t>SPACE_DEFENSE</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr"/>
-      <c r="E22" s="11" t="n">
-        <v>0</v>
-      </c>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
@@ -3834,7 +3719,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>시장별 P10 하한 (코드 산출값 — 대조 상대)</t>
+          <t>시장별 P10 하한 (직접 산출)</t>
         </is>
       </c>
     </row>
@@ -3844,9 +3729,7 @@
           <t>KR</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>73914096486.05334</v>
-      </c>
+      <c r="B25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -3854,26 +3737,38 @@
           <t>US</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
-        <v>308975201.0855556</v>
-      </c>
+      <c r="B26" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>※ 붉은 칸 3종목이 경계사례다. KTOS 는 하한 대비 -0.5%, SPCX 는 시즈닝 미달, 010120 은 정지·분할.</t>
+          <t>※ 붉은 칸 3종목이 경계사례다. 010120 은 정지·분할, SPCX 는 시즈닝 미달, KTOS 는 하한 근접.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>※ ⑥ 총합이 정확히 1.0 인지 반드시 검산한다(룰북 §14 비중합계 100%).</t>
+          <t>※ ①②는 L2 방식으로 18종목 전부 계산해야 한다. 표본 1종목만 하고 나머지는 넘기지 말 것 —</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P10 은 시장별 전체 분포에서 나오므로 한 종목만으로는 하한 자체를 못 구한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>※ ⑧ 총합이 정확히 1.0 인지 반드시 검산한다(룰북 §14 비중합계 100%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>※ 빈 셀이 생기면 같은 테마의 타지역 셀로 재배분한다(룰북 §10, D-10 ③).</t>
         </is>
@@ -3890,16 +3785,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:T47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
@@ -3910,6 +3805,9 @@
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3929,7 +3827,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>구성종목과 목표비중 (코드 산출값)</t>
+          <t>구성종목과 목표비중 — L3 ⑤⑧ 에서 직접 산출한 값을 옮겨 적는다</t>
         </is>
       </c>
     </row>
@@ -3946,816 +3844,878 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>목표비중</t>
+          <t>① 편입?</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>② 목표비중</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>010120</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>012450</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>018260</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>064350</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>064400</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>079550</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>267260</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>298040</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>307950</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>APH</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>ATI</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>GEV</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>KTOS</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>TER</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>일별 원자료 — 유니버스 18종목 원종가 (KR 원화 / US 달러) + 환율</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>환율(원/달러)</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>010120</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>012450</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>018260</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>064350</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>064400</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>079550</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>267260</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>298040</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>307950</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
         <is>
           <t>ANET</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>ALAB</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>010120</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>267260</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>298040</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>APH</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>ATI</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
         <is>
           <t>GEV</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>ETN</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>APH</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>012450</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>064350</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>079550</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>0.0555555555555555</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>KTOS</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>0.1666666666666666</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>일별 원자료 — 종목별 원종가 (KR 원화 / US 달러) + 환율</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>환율(원/달러)</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>064400</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>307950</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="T26" s="6" t="inlineStr">
         <is>
           <t>TER</t>
         </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>ANET</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>ALAB</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>010120</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>267260</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>298040</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>GEV</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>ETN</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>APH</t>
-        </is>
-      </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>012450</t>
-        </is>
-      </c>
-      <c r="O23" s="6" t="inlineStr">
-        <is>
-          <t>064350</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>079550</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>KTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n">
-        <v>1507.2</v>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>57100</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>370000</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>320.48</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>133.64</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>118.99</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>788000</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>891000</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>2610000</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>910.75</v>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>368.85</v>
-      </c>
-      <c r="M24" s="9" t="n">
-        <v>128.38</v>
-      </c>
-      <c r="N24" s="9" t="n">
-        <v>1537000</v>
-      </c>
-      <c r="O24" s="9" t="n">
-        <v>211000</v>
-      </c>
-      <c r="P24" s="9" t="n">
-        <v>827000</v>
-      </c>
-      <c r="Q24" s="9" t="n">
-        <v>71.95999999999999</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>1506.8</v>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>61400</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>415500</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>358.29</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>145.07</v>
-      </c>
-      <c r="G25" s="9" t="n">
-        <v>125.46</v>
-      </c>
-      <c r="H25" s="9" t="n">
-        <v>788000</v>
-      </c>
-      <c r="I25" s="9" t="n">
-        <v>980000</v>
-      </c>
-      <c r="J25" s="9" t="n">
-        <v>2930000</v>
-      </c>
-      <c r="K25" s="9" t="n">
-        <v>936.0700000000001</v>
-      </c>
-      <c r="L25" s="9" t="n">
-        <v>385.58</v>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>135.32</v>
-      </c>
-      <c r="N25" s="9" t="n">
-        <v>1484000</v>
-      </c>
-      <c r="O25" s="9" t="n">
-        <v>206500</v>
-      </c>
-      <c r="P25" s="9" t="n">
-        <v>833000</v>
-      </c>
-      <c r="Q25" s="9" t="n">
-        <v>74.45999999999999</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n">
-        <v>1476.1</v>
-      </c>
-      <c r="C26" s="9" t="n">
-        <v>63000</v>
-      </c>
-      <c r="D26" s="9" t="n">
-        <v>393500</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>364.21</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>146.05</v>
-      </c>
-      <c r="G26" s="9" t="n">
-        <v>129.46</v>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>788000</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>980000</v>
-      </c>
-      <c r="J26" s="9" t="n">
-        <v>2882000</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>968.02</v>
-      </c>
-      <c r="L26" s="9" t="n">
-        <v>400.44</v>
-      </c>
-      <c r="M26" s="9" t="n">
-        <v>137.68</v>
-      </c>
-      <c r="N26" s="9" t="n">
-        <v>1451000</v>
-      </c>
-      <c r="O26" s="9" t="n">
-        <v>203000</v>
-      </c>
-      <c r="P26" s="9" t="n">
-        <v>887000</v>
-      </c>
-      <c r="Q26" s="9" t="n">
-        <v>68.33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>1481.1</v>
+        <v>1507.2</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>63300</v>
+        <v>788000</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>391500</v>
+        <v>1537000</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>367.99</v>
+        <v>151300</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>147.35</v>
+        <v>211000</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>149.05</v>
+        <v>57100</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>788000</v>
+        <v>827000</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>999000</v>
+        <v>891000</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>2940000</v>
+        <v>2610000</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>991.3200000000001</v>
+        <v>370000</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>403</v>
+        <v>118.99</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>140.75</v>
+        <v>133.64</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>1507000</v>
+        <v>128.38</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>210000</v>
+        <v>147.28</v>
       </c>
       <c r="P27" s="9" t="n">
-        <v>921000</v>
+        <v>368.85</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>70.34</v>
+        <v>910.75</v>
+      </c>
+      <c r="R27" s="9" t="n">
+        <v>71.95999999999999</v>
+      </c>
+      <c r="S27" s="9" t="n"/>
+      <c r="T27" s="9" t="n">
+        <v>320.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>1479.8</v>
+        <v>1506.8</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>60900</v>
+        <v>788000</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>388000</v>
+        <v>1484000</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>370.13</v>
+        <v>154000</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>152.02</v>
+        <v>206500</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>166.795</v>
+        <v>61400</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>179200</v>
+        <v>833000</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>1007000</v>
+        <v>980000</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>3058000</v>
+        <v>2930000</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>991.12</v>
+        <v>415500</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>403.36</v>
+        <v>125.46</v>
       </c>
       <c r="M28" s="9" t="n">
-        <v>145.27</v>
+        <v>145.07</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>1530000</v>
+        <v>135.32</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>207000</v>
+        <v>156.39</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>939000</v>
+        <v>385.58</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>73.55</v>
+        <v>936.0700000000001</v>
+      </c>
+      <c r="R28" s="9" t="n">
+        <v>74.45999999999999</v>
+      </c>
+      <c r="S28" s="9" t="n"/>
+      <c r="T28" s="9" t="n">
+        <v>358.29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>1476.1</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>788000</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>1451000</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>148300</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>203000</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>63000</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>887000</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>980000</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>2882000</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>393500</v>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>129.46</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>146.05</v>
+      </c>
+      <c r="N29" s="9" t="n">
+        <v>137.68</v>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>159.63</v>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>400.44</v>
+      </c>
+      <c r="Q29" s="9" t="n">
+        <v>968.02</v>
+      </c>
+      <c r="R29" s="9" t="n">
+        <v>68.33</v>
+      </c>
+      <c r="S29" s="9" t="n"/>
+      <c r="T29" s="9" t="n">
+        <v>364.21</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>1481.1</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>788000</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>1507000</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>148700</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>210000</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>63300</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>921000</v>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>999000</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>2940000</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>391500</v>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>149.05</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>147.35</v>
+      </c>
+      <c r="N30" s="9" t="n">
+        <v>140.75</v>
+      </c>
+      <c r="O30" s="9" t="n">
+        <v>162.21</v>
+      </c>
+      <c r="P30" s="9" t="n">
+        <v>403</v>
+      </c>
+      <c r="Q30" s="9" t="n">
+        <v>991.3200000000001</v>
+      </c>
+      <c r="R30" s="9" t="n">
+        <v>70.34</v>
+      </c>
+      <c r="S30" s="9" t="n"/>
+      <c r="T30" s="9" t="n">
+        <v>367.99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>1479.8</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>179200</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>1530000</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>148700</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>207000</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>60900</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>939000</v>
+      </c>
+      <c r="I31" s="9" t="n">
+        <v>1007000</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>3058000</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>388000</v>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>166.795</v>
+      </c>
+      <c r="M31" s="9" t="n">
+        <v>152.02</v>
+      </c>
+      <c r="N31" s="9" t="n">
+        <v>145.27</v>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>163.78</v>
+      </c>
+      <c r="P31" s="9" t="n">
+        <v>403.36</v>
+      </c>
+      <c r="Q31" s="9" t="n">
+        <v>991.12</v>
+      </c>
+      <c r="R31" s="9" t="n">
+        <v>73.55</v>
+      </c>
+      <c r="S31" s="9" t="n"/>
+      <c r="T31" s="9" t="n">
+        <v>370.13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n">
+      <c r="B32" s="9" t="n">
         <v>1489.8</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C32" s="9" t="n">
+        <v>185600</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>1523000</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>151500</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>211500</v>
+      </c>
+      <c r="G32" s="9" t="n">
         <v>62000</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="H32" s="9" t="n">
+        <v>934000</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>1061000</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>3042000</v>
+      </c>
+      <c r="K32" s="9" t="n">
         <v>401000</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="L32" s="9" t="n">
+        <v>170.6</v>
+      </c>
+      <c r="M32" s="9" t="n">
+        <v>154.37</v>
+      </c>
+      <c r="N32" s="9" t="n">
+        <v>148.72</v>
+      </c>
+      <c r="O32" s="9" t="n">
+        <v>163.03</v>
+      </c>
+      <c r="P32" s="9" t="n">
+        <v>401.9</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>987.5</v>
+      </c>
+      <c r="R32" s="9" t="n">
+        <v>73.66</v>
+      </c>
+      <c r="S32" s="9" t="n"/>
+      <c r="T32" s="9" t="n">
         <v>365.51</v>
       </c>
-      <c r="F29" s="9" t="n">
-        <v>154.37</v>
-      </c>
-      <c r="G29" s="9" t="n">
-        <v>170.6</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>185600</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>1061000</v>
-      </c>
-      <c r="J29" s="9" t="n">
-        <v>3042000</v>
-      </c>
-      <c r="K29" s="9" t="n">
-        <v>987.5</v>
-      </c>
-      <c r="L29" s="9" t="n">
-        <v>401.9</v>
-      </c>
-      <c r="M29" s="9" t="n">
-        <v>148.72</v>
-      </c>
-      <c r="N29" s="9" t="n">
-        <v>1523000</v>
-      </c>
-      <c r="O29" s="9" t="n">
-        <v>211500</v>
-      </c>
-      <c r="P29" s="9" t="n">
-        <v>934000</v>
-      </c>
-      <c r="Q29" s="9" t="n">
-        <v>73.66</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>수기 산출</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>① KR 다리 수익률</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>② US 다리 수익률(원화)</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>③ 합산 지수수익률</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>④ 지수레벨</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>코드 지수레벨</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>⑤ 일치?</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="10" t="n">
-        <v>1023.801566757947</v>
-      </c>
-      <c r="G33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="10" t="n">
-        <v>1076.495915509196</v>
-      </c>
-      <c r="G34" s="8" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="10" t="n">
-        <v>1057.307314585083</v>
-      </c>
-      <c r="G35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
-      <c r="F36" s="10" t="n">
-        <v>1087.217428758063</v>
-      </c>
-      <c r="G36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
-      <c r="F37" s="10" t="n">
-        <v>1065.255617307987</v>
-      </c>
-      <c r="G37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
-      <c r="F38" s="10" t="n">
-        <v>1080.971143677037</v>
-      </c>
-      <c r="G38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>※ KR 다리부터 하라. 환율이 안 들어가므로 미결(B-2 적용시점·B-3 결측일)에 걸리지 않는다.</t>
-        </is>
-      </c>
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>※ US 다리는 '당일 환율 적용'을 가정하고 계산한 뒤, 불일치가 나면 그것이 B-2·B-3 때문인지 판별한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>※ 2026-04-13 은 010120 분할일이다. 규칙대로 원종가를 쓰면 -77% 가 나오고 코드와 '일치'한다.</t>
-        </is>
-      </c>
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>※ KR 다리부터 하라. 환율이 안 들어가므로 미결(B-2 적용시점·B-3 결측일)에 걸리지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>※ US 다리는 '당일 환율 적용'을 가정하고 계산한 뒤, 불일치가 나면 그것이 B-2·B-3 때문인지 판별한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>※ 구간 내 리밸런싱이 0회이므로 연결계수·제수(B-1)는 발동하지 않는다. 효력발생일 대비 가격비만 쓴다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>※ 2026-04-13 은 010120 분할일이다. 규칙대로 원종가를 쓰면 -77% 가 나오고 코드와 '일치'한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   → 5_대조표 의 (d) 칸에 '규칙 적용 결과 일치 / 경제적 타당성 불가'로 나눠 적을 것.</t>
         </is>

--- a/06_코드/qa/manual_check/J5_수기검산_워크시트.xlsx
+++ b/06_코드/qa/manual_check/J5_수기검산_워크시트.xlsx
@@ -695,7 +695,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  → 순서: ① 노란 칸 전부 채움  ② 파일 저장  ③ 봉인 파일 열기  ④ 08 대조표에 옮겨 적기</t>
+          <t xml:space="preserve">  → 순서: ① 노란 칸 전부 채움  ② 파일 저장  ③ 봉인 파일 열기  ④ 09 대조표에 옮겨 적기</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       <c r="B26" s="12" t="n"/>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>← 이 값을 08 대조표로 옮깁니다</t>
+          <t>← 이 값을 09 대조표로 옮깁니다</t>
         </is>
       </c>
     </row>

--- a/06_코드/qa/manual_check/J5_수기검산_워크시트.xlsx
+++ b/06_코드/qa/manual_check/J5_수기검산_워크시트.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -925,209 +925,349 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>입력 스냅샷 지문 — 이 워크북이 어느 파일을 보고 만들어졌는지</t>
+          <t>적용 규칙 — 2026-07-30 의결분 (파일럿 범위 한정)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>파일</t>
+          <t>항목</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>SHA-256 (앞 16자리)</t>
+          <t>의결 규칙</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>행 수</t>
+          <t>범위·유보</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>daily_market_state.csv</t>
+          <t>환율 적용시점</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>4bc15889822e5032</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="n">
-        <v>3303</v>
+          <t>평가일 당일 ECOS — 지수·미국 BM 동일 적용</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>계열코드 공식성 PROVISIONAL</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>adtv90_ledger.csv</t>
+          <t>산출일</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>89673845cda2d5af</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="n">
-        <v>36</v>
+          <t>COMMON_OPEN_DAYS_PILOT (한·미 공통 개장일)</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>합집합·가격이월은 후속 적용시험</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>constituents_2026-06-30.csv</t>
+          <t>연결 방식</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>38baa5ce6aede302</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="n">
-        <v>18</v>
+          <t>CHAIN_REBASE_PILOT (연결계수)</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>이번 구간 미발동 — 정확성 실증 아님</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>weights_2026-03-31.csv</t>
+          <t>기업행사</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>7b382c2a0aadd5cc</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>index_vs_benchmark.csv</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>f188f3f5fb5a7a75</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="n">
-        <v>59</v>
+          <t>액면가 기준 5:1 · 경계일 신주권상장일</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>010120 개별 사건 판정 · 일반화 보류</t>
+        </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>calendar.csv</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>3cbb2c8d960a3c7a</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="n">
-        <v>392</v>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>■ 의결됐다고 검산이 필요 없어지는 것은 아닙니다 — 확인할 것이 바뀝니다.</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>fx.csv</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>ef833251ecf38c06</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="n">
-        <v>181</v>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  의결 전:  룰북에서 규칙을 직접 도출해 보십시오.</t>
+        </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>※ 나중에 산출물이 바뀌면 이 지문이 달라집니다. 검산 결과가 어느 버전에 대한 것인지 이것으로 특정합니다.</t>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  의결 후:  의결 규칙을 적용하되, 그 규칙이 룰북에서 실제로 도출되는지 확인하십시오.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  도출되지 않으면 그것이 발견사항입니다. 의결됐다는 이유로 넘기지 마십시오.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>작성자 기록</t>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  환율 항목은 QA 보고(당일 환율만 공표 지수를 재현함)가 의결 근거의 일부였습니다.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>작성자</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>시작 일시</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="n"/>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  즉 이 항목은 QA 와 완전히 독립적인 확인이 아닙니다. 그 한계를 알고 보십시오.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>완료 일시</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n"/>
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>입력 스냅샷 지문 — 이 워크북이 어느 파일을 보고 만들어졌는지</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>봉인 개봉 일시</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n"/>
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>파일</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>SHA-256 (앞 16자리)</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>행 수</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
+          <t>daily_market_state.csv</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>4bc15889822e5032</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>3303</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>adtv90_ledger.csv</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>89673845cda2d5af</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>constituents_2026-06-30.csv</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>38baa5ce6aede302</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>weights_2026-03-31.csv</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>7b382c2a0aadd5cc</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>index_vs_benchmark.csv</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>f188f3f5fb5a7a75</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>calendar.csv</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>3cbb2c8d960a3c7a</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>fx.csv</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>ef833251ecf38c06</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>※ 나중에 산출물이 바뀌면 이 지문이 달라집니다. 검산 결과가 어느 버전에 대한 것인지 이것으로 특정합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>작성자 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>작성자</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>시작 일시</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>완료 일시</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>봉인 개봉 일시</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
           <t>사용한 도구(엑셀/계산기 등)</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
+      <c r="B68" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="27">
     <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="B67:D67"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A61:H61"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A16:H16"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A27:H27"/>
-    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B64:D64"/>
     <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="B50:D50"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A47:H47"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="B54:D54"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B66:D66"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="B52:D52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
